--- a/data/registros_projetos.xlsx
+++ b/data/registros_projetos.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marcos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -551,17 +552,95 @@
           <t>Projetos Básicos</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>473779.12</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>473779.12</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>data_prevista</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>data_realizada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>observacoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contratual</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Concluído</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/registros_projetos.xlsx
+++ b/data/registros_projetos.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,6 +610,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>idp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>observacoes</t>
         </is>
       </c>
@@ -617,7 +622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Assinatura do contrato</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -625,14 +630,10 @@
           <t>Contratual</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -641,6 +642,36 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordem de serviço</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Contratual</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Emitida</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Início da execução</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
